--- a/테이블/몬스터/몬스터 스트링 테이블.xlsx
+++ b/테이블/몬스터/몬스터 스트링 테이블.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\addmin\Desktop\Unreal\Project TirgerGhostField\기획\테이블\몬스터\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74B4E447-84ED-4388-A5CE-6BCC33CFEE69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5300BC95-B5CE-4043-85AB-08C33A5143B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="25">
   <si>
     <t>속성 명칭</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -128,6 +128,20 @@
   </si>
   <si>
     <t>""</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산적</t>
+  </si>
+  <si>
+    <t>고을의 인근을 떠도는 산적이다. 이성을 잃고 미쳐버려, 대화 따위는 안 통하는 것 같다.</t>
+  </si>
+  <si>
+    <t>방황하고, 떠돈다. 그 자체로도 갈증이다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산적은 직관적이고 단순하게 공격합니다. 방어와 공격을 적절하게 활용해 공격하십시오.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -649,13 +663,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72C19B3A-9DE6-4959-8646-89E4535BEFF0}">
-  <dimension ref="B1:F1"/>
+  <dimension ref="B1:F4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="9.375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="15.875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="37.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="80.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="81.875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.25" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.375" bestFit="1" customWidth="1"/>
   </cols>
@@ -682,6 +697,57 @@
         <v>정보 텍스트</v>
       </c>
     </row>
+    <row r="2" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B2">
+        <v>1000</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B3">
+        <v>1001</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B4">
+        <v>1002</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" t="s">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
